--- a/public/sap-reporting/expansion-150-downloads/EXT-PP08-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-PP08-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rd51e1b75042f4c91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Reb244fd53caf4a03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R82aa4897798c4829"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R0cb2d5318d444be6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R0580cd4e6c344b7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rf2c2ea788caa4674"/>
   </x:sheets>
 </x:workbook>
 </file>
